--- a/portfolio_model/data/input/example_portfolio_minimal.xlsx
+++ b/portfolio_model/data/input/example_portfolio_minimal.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Positions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +28,42 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00444444"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C5700"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +78,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,59 +453,518 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Example portfolio — minimal (ticker + weight only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Copy this file, replace the rows, run: python main.py --input data/input/your_file.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>VOO</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>IEF</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B8" s="4" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>How to use this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>This is an EXAMPLE input file. Copy it, replace the rows with your own holdings, and run:  python main.py --input data/input/your_file.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1. The only required columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Ticker, plus ONE of: Portfolio Weight | Market Value | Shares and Price. Everything else improves the analysis but is optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2. Column reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>What it does</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Accepted header names</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Identifies the holding and its price series</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ticker, symbol, security, company, name</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>one of three</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The allocation being analysed (must sum to 1.0)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>portfolio weight, weight, % of portfolio</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Market Value</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>one of three</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Weights derived as value / total</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>market value, current value, value</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shares + Price</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>one of three</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Weights derived from shares x price</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>shares, quantity | current price, last price</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Asset Class</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Drives equity / bond / cash logic and stress mapping</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>asset class, class, bucket, type</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sector caps and sector attribution</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>sector, GICS sector, industry sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Expected Return</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>The central simulation assumption</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>expected return, exp return, mean return</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Dispersion used by every engine</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>volatility, std dev, stdev, risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Investment Thesis</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Missing theses become governance flags</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>investment thesis, thesis, why own</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Target Weight</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Enables drift-vs-target flags</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>target weight, target allocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Correlation Group</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Enables correlated-group exposure caps</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>correlation group, group, cluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cost Basis</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Enables dollar P&amp;L</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>cost basis, avg cost, average cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Non-USD rows are excluded and reported</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>currency, ccy</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>3. Formats the reader accepts</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Weights: 0.15, 15%, 15 % and 0.1500 all mean 15%.  Money: $1,234.50 and 1,234.50 both work.  Negatives: (450) is read as -450.  Tickers must look like ADBE, BRK.B, 6752.T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>4. Things that will make the run fail (deliberately included so you can see the messages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>A company name instead of a ticker is skipped and reported. Formulas with no cached values are reported with instructions to re-save the file in Excel/LibreOffice. Weights that do not sum to 1.0 are renormalised and the run says so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>5. Try these three runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>python main.py --input data/input/example_portfolio_full.xlsx --offline</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>python main.py --input data/input/example_portfolio_full.xlsx --offline --glide-method none</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>python main.py --input data/input/example_portfolio_full.xlsx --offline --model student_t</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Compare Probability reserve fully funded and CVaR 95% across the three runs. That comparison is the model explaining itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>6. Where every number is defined</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>docs/METRIC_DEFINITIONS.md, the Definitions sheet of the OUTPUT workbook, and the Definitions tab of the web UI - all generated from portfolio_model/src/metric_glossary.py.</t>
+        </is>
       </c>
     </row>
   </sheetData>
